--- a/master-slave/outputs/exp1-full/runs_delta.xlsx
+++ b/master-slave/outputs/exp1-full/runs_delta.xlsx
@@ -49437,9 +49437,18 @@
       <c r="H1167" t="n">
         <v>3746.459096600642</v>
       </c>
+      <c r="I1167" t="n">
+        <v>3734.637864190819</v>
+      </c>
+      <c r="J1167" t="n">
+        <v>0.3155308013518449</v>
+      </c>
       <c r="K1167" t="n">
         <v>54662929032</v>
       </c>
+      <c r="L1167" t="n">
+        <v>57124025080</v>
+      </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
@@ -49470,9 +49479,18 @@
       <c r="H1168" t="n">
         <v>3712.551616640903</v>
       </c>
+      <c r="I1168" t="n">
+        <v>3701.426238341227</v>
+      </c>
+      <c r="J1168" t="n">
+        <v>0.299669323109429</v>
+      </c>
       <c r="K1168" t="n">
         <v>54809094607</v>
       </c>
+      <c r="L1168" t="n">
+        <v>57505634483</v>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -49503,9 +49521,18 @@
       <c r="H1169" t="n">
         <v>3724.489476987844</v>
       </c>
+      <c r="I1169" t="n">
+        <v>3717.850219879201</v>
+      </c>
+      <c r="J1169" t="n">
+        <v>0.178259521195183</v>
+      </c>
       <c r="K1169" t="n">
         <v>54759404675</v>
       </c>
+      <c r="L1169" t="n">
+        <v>57762529819</v>
+      </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
@@ -49536,9 +49563,18 @@
       <c r="H1170" t="n">
         <v>3722.164180205413</v>
       </c>
+      <c r="I1170" t="n">
+        <v>3721.377685106203</v>
+      </c>
+      <c r="J1170" t="n">
+        <v>0.02113004857208739</v>
+      </c>
       <c r="K1170" t="n">
         <v>54598042516</v>
       </c>
+      <c r="L1170" t="n">
+        <v>57320554506</v>
+      </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
@@ -49569,9 +49605,18 @@
       <c r="H1171" t="n">
         <v>3733.340975642415</v>
       </c>
+      <c r="I1171" t="n">
+        <v>3752.059186104953</v>
+      </c>
+      <c r="J1171" t="n">
+        <v>-0.5013796110417464</v>
+      </c>
       <c r="K1171" t="n">
         <v>54951260017</v>
       </c>
+      <c r="L1171" t="n">
+        <v>57452622269</v>
+      </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
@@ -49812,9 +49857,18 @@
       <c r="H1177" t="n">
         <v>3700.833521391454</v>
       </c>
+      <c r="I1177" t="n">
+        <v>3723.618060129096</v>
+      </c>
+      <c r="J1177" t="n">
+        <v>-0.6156596508852229</v>
+      </c>
       <c r="K1177" t="n">
         <v>54676570942</v>
       </c>
+      <c r="L1177" t="n">
+        <v>56904516140</v>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -49845,9 +49899,18 @@
       <c r="H1178" t="n">
         <v>3737.531688329461</v>
       </c>
+      <c r="I1178" t="n">
+        <v>3732.098359156955</v>
+      </c>
+      <c r="J1178" t="n">
+        <v>0.1453721232510697</v>
+      </c>
       <c r="K1178" t="n">
         <v>54630006030</v>
       </c>
+      <c r="L1178" t="n">
+        <v>57480638774</v>
+      </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
@@ -49878,9 +49941,18 @@
       <c r="H1179" t="n">
         <v>3701.454862113157</v>
       </c>
+      <c r="I1179" t="n">
+        <v>3685.393036567049</v>
+      </c>
+      <c r="J1179" t="n">
+        <v>0.4339327681802099</v>
+      </c>
       <c r="K1179" t="n">
         <v>55075525454</v>
       </c>
+      <c r="L1179" t="n">
+        <v>57577664139</v>
+      </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
@@ -49911,9 +49983,18 @@
       <c r="H1180" t="n">
         <v>3701.038233464449</v>
       </c>
+      <c r="I1180" t="n">
+        <v>3715.358974128856</v>
+      </c>
+      <c r="J1180" t="n">
+        <v>-0.3869384686415851</v>
+      </c>
       <c r="K1180" t="n">
         <v>54950125042</v>
       </c>
+      <c r="L1180" t="n">
+        <v>57463623038</v>
+      </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
@@ -49944,9 +50025,18 @@
       <c r="H1181" t="n">
         <v>3715.729199532919</v>
       </c>
+      <c r="I1181" t="n">
+        <v>3691.1715151923</v>
+      </c>
+      <c r="J1181" t="n">
+        <v>0.6609115740648115</v>
+      </c>
       <c r="K1181" t="n">
         <v>54303352544</v>
       </c>
+      <c r="L1181" t="n">
+        <v>56967380451</v>
+      </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
@@ -50187,9 +50277,18 @@
       <c r="H1187" t="n">
         <v>3675.950951253969</v>
       </c>
+      <c r="I1187" t="n">
+        <v>3689.49674612381</v>
+      </c>
+      <c r="J1187" t="n">
+        <v>-0.368497704389131</v>
+      </c>
       <c r="K1187" t="n">
         <v>55095800349</v>
       </c>
+      <c r="L1187" t="n">
+        <v>57912805156</v>
+      </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
@@ -50220,9 +50319,18 @@
       <c r="H1188" t="n">
         <v>3681.728201160339</v>
       </c>
+      <c r="I1188" t="n">
+        <v>3659.596599670127</v>
+      </c>
+      <c r="J1188" t="n">
+        <v>0.6011199165445265</v>
+      </c>
       <c r="K1188" t="n">
         <v>55476519613</v>
       </c>
+      <c r="L1188" t="n">
+        <v>58294075797</v>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
@@ -50253,9 +50361,18 @@
       <c r="H1189" t="n">
         <v>3699.34610647119</v>
       </c>
+      <c r="I1189" t="n">
+        <v>3707.084407050092</v>
+      </c>
+      <c r="J1189" t="n">
+        <v>-0.209180226888356</v>
+      </c>
       <c r="K1189" t="n">
         <v>55168729495</v>
       </c>
+      <c r="L1189" t="n">
+        <v>57776682642</v>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
@@ -50286,9 +50403,18 @@
       <c r="H1190" t="n">
         <v>3686.45567627628</v>
       </c>
+      <c r="I1190" t="n">
+        <v>3670.155654060006</v>
+      </c>
+      <c r="J1190" t="n">
+        <v>0.4421597232585864</v>
+      </c>
       <c r="K1190" t="n">
         <v>55151096875</v>
       </c>
+      <c r="L1190" t="n">
+        <v>57893866011</v>
+      </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
@@ -50319,9 +50445,18 @@
       <c r="H1191" t="n">
         <v>3712.571582138261</v>
       </c>
+      <c r="I1191" t="n">
+        <v>3694.323624704174</v>
+      </c>
+      <c r="J1191" t="n">
+        <v>0.4915179958247826</v>
+      </c>
       <c r="K1191" t="n">
         <v>55097006370</v>
       </c>
+      <c r="L1191" t="n">
+        <v>58164998703</v>
+      </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
@@ -50562,9 +50697,18 @@
       <c r="H1197" t="n">
         <v>3671.789267733619</v>
       </c>
+      <c r="I1197" t="n">
+        <v>3640.740116322532</v>
+      </c>
+      <c r="J1197" t="n">
+        <v>0.8456136544636614</v>
+      </c>
       <c r="K1197" t="n">
         <v>55592915338</v>
       </c>
+      <c r="L1197" t="n">
+        <v>58493629954</v>
+      </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
@@ -50595,9 +50739,18 @@
       <c r="H1198" t="n">
         <v>3661.915773637411</v>
       </c>
+      <c r="I1198" t="n">
+        <v>3654.125937455555</v>
+      </c>
+      <c r="J1198" t="n">
+        <v>0.21272570597982</v>
+      </c>
       <c r="K1198" t="n">
         <v>55832302836</v>
       </c>
+      <c r="L1198" t="n">
+        <v>58646685244</v>
+      </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
@@ -50628,9 +50781,18 @@
       <c r="H1199" t="n">
         <v>3669.840810726894</v>
       </c>
+      <c r="I1199" t="n">
+        <v>3679.791601574635</v>
+      </c>
+      <c r="J1199" t="n">
+        <v>-0.2711504765725617</v>
+      </c>
       <c r="K1199" t="n">
         <v>55777809317</v>
       </c>
+      <c r="L1199" t="n">
+        <v>58689620376</v>
+      </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
@@ -50661,9 +50823,18 @@
       <c r="H1200" t="n">
         <v>3693.94371769767</v>
       </c>
+      <c r="I1200" t="n">
+        <v>3688.473541710137</v>
+      </c>
+      <c r="J1200" t="n">
+        <v>0.1480849846554326</v>
+      </c>
       <c r="K1200" t="n">
         <v>56129453598</v>
       </c>
+      <c r="L1200" t="n">
+        <v>58587308667</v>
+      </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
@@ -50694,9 +50865,18 @@
       <c r="H1201" t="n">
         <v>3634.221390650036</v>
       </c>
+      <c r="I1201" t="n">
+        <v>3622.171226928838</v>
+      </c>
+      <c r="J1201" t="n">
+        <v>0.3315748388967273</v>
+      </c>
       <c r="K1201" t="n">
         <v>55857258078</v>
       </c>
+      <c r="L1201" t="n">
+        <v>58504648649</v>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
@@ -50937,9 +51117,18 @@
       <c r="H1207" t="n">
         <v>7950.820550352748</v>
       </c>
+      <c r="I1207" t="n">
+        <v>7896.665916824827</v>
+      </c>
+      <c r="J1207" t="n">
+        <v>0.6811200577972825</v>
+      </c>
       <c r="K1207" t="n">
         <v>75912438625</v>
       </c>
+      <c r="L1207" t="n">
+        <v>80237816239</v>
+      </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
@@ -50970,9 +51159,18 @@
       <c r="H1208" t="n">
         <v>7955.829434580442</v>
       </c>
+      <c r="I1208" t="n">
+        <v>7927.850538585521</v>
+      </c>
+      <c r="J1208" t="n">
+        <v>0.3516779265441417</v>
+      </c>
       <c r="K1208" t="n">
         <v>75788713258</v>
       </c>
+      <c r="L1208" t="n">
+        <v>80159523154</v>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
@@ -51003,9 +51201,18 @@
       <c r="H1209" t="n">
         <v>7922.295579699436</v>
       </c>
+      <c r="I1209" t="n">
+        <v>7909.028059047647</v>
+      </c>
+      <c r="J1209" t="n">
+        <v>0.1674706594612083</v>
+      </c>
       <c r="K1209" t="n">
         <v>75901553919</v>
       </c>
+      <c r="L1209" t="n">
+        <v>80700855233</v>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
@@ -51036,9 +51243,18 @@
       <c r="H1210" t="n">
         <v>7929.080911495736</v>
       </c>
+      <c r="I1210" t="n">
+        <v>7941.207196330872</v>
+      </c>
+      <c r="J1210" t="n">
+        <v>-0.1529343056337747</v>
+      </c>
       <c r="K1210" t="n">
         <v>75863869312</v>
       </c>
+      <c r="L1210" t="n">
+        <v>80308231802</v>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
@@ -51069,9 +51285,18 @@
       <c r="H1211" t="n">
         <v>7925.45930514813</v>
       </c>
+      <c r="I1211" t="n">
+        <v>7882.516490978265</v>
+      </c>
+      <c r="J1211" t="n">
+        <v>0.5418337602461752</v>
+      </c>
       <c r="K1211" t="n">
         <v>75960176548</v>
       </c>
+      <c r="L1211" t="n">
+        <v>80392234536</v>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
@@ -51312,9 +51537,18 @@
       <c r="H1217" t="n">
         <v>7971.19944637468</v>
       </c>
+      <c r="I1217" t="n">
+        <v>7950.031382857865</v>
+      </c>
+      <c r="J1217" t="n">
+        <v>0.2655568168783214</v>
+      </c>
       <c r="K1217" t="n">
         <v>75446297308</v>
       </c>
+      <c r="L1217" t="n">
+        <v>80122645190</v>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
@@ -51345,9 +51579,18 @@
       <c r="H1218" t="n">
         <v>7946.640807827146</v>
       </c>
+      <c r="I1218" t="n">
+        <v>7972.351867932245</v>
+      </c>
+      <c r="J1218" t="n">
+        <v>-0.3235462722786537</v>
+      </c>
       <c r="K1218" t="n">
         <v>75276243496</v>
       </c>
+      <c r="L1218" t="n">
+        <v>79784785456</v>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
@@ -51378,9 +51621,18 @@
       <c r="H1219" t="n">
         <v>7987.275227344298</v>
       </c>
+      <c r="I1219" t="n">
+        <v>7971.672730803499</v>
+      </c>
+      <c r="J1219" t="n">
+        <v>0.1953419169454026</v>
+      </c>
       <c r="K1219" t="n">
         <v>75178609291</v>
       </c>
+      <c r="L1219" t="n">
+        <v>79522818858</v>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
@@ -51411,9 +51663,18 @@
       <c r="H1220" t="n">
         <v>7948.726835636515</v>
       </c>
+      <c r="I1220" t="n">
+        <v>7952.71583708755</v>
+      </c>
+      <c r="J1220" t="n">
+        <v>-0.05018415569587491</v>
+      </c>
       <c r="K1220" t="n">
         <v>75465058292</v>
       </c>
+      <c r="L1220" t="n">
+        <v>79775892073</v>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
@@ -51444,9 +51705,18 @@
       <c r="H1221" t="n">
         <v>7973.815100914153</v>
       </c>
+      <c r="I1221" t="n">
+        <v>7927.888438271992</v>
+      </c>
+      <c r="J1221" t="n">
+        <v>0.5759684926340478</v>
+      </c>
       <c r="K1221" t="n">
         <v>75293852541</v>
       </c>
+      <c r="L1221" t="n">
+        <v>79511459580</v>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
@@ -51687,9 +51957,18 @@
       <c r="H1227" t="n">
         <v>7880.649034908736</v>
       </c>
+      <c r="I1227" t="n">
+        <v>7882.421883289733</v>
+      </c>
+      <c r="J1227" t="n">
+        <v>-0.02249622300325519</v>
+      </c>
       <c r="K1227" t="n">
         <v>67519046491</v>
       </c>
+      <c r="L1227" t="n">
+        <v>79565053358</v>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
@@ -51720,9 +51999,18 @@
       <c r="H1228" t="n">
         <v>7898.118755099087</v>
       </c>
+      <c r="I1228" t="n">
+        <v>7894.218990355931</v>
+      </c>
+      <c r="J1228" t="n">
+        <v>0.04937586866034858</v>
+      </c>
       <c r="K1228" t="n">
         <v>73153473252</v>
       </c>
+      <c r="L1228" t="n">
+        <v>79896102464</v>
+      </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
@@ -51753,9 +52041,18 @@
       <c r="H1229" t="n">
         <v>7865.5925004317</v>
       </c>
+      <c r="I1229" t="n">
+        <v>7854.587626719945</v>
+      </c>
+      <c r="J1229" t="n">
+        <v>0.139911566880066</v>
+      </c>
       <c r="K1229" t="n">
         <v>75330589143</v>
       </c>
+      <c r="L1229" t="n">
+        <v>79930904482</v>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
@@ -51786,9 +52083,18 @@
       <c r="H1230" t="n">
         <v>7870.972885162075</v>
       </c>
+      <c r="I1230" t="n">
+        <v>7880.753608111032</v>
+      </c>
+      <c r="J1230" t="n">
+        <v>-0.1242632021690136</v>
+      </c>
       <c r="K1230" t="n">
         <v>75268039891</v>
       </c>
+      <c r="L1230" t="n">
+        <v>80047716807</v>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
@@ -51819,9 +52125,18 @@
       <c r="H1231" t="n">
         <v>7893.567618540175</v>
       </c>
+      <c r="I1231" t="n">
+        <v>7857.937480843023</v>
+      </c>
+      <c r="J1231" t="n">
+        <v>0.4513819279062784</v>
+      </c>
       <c r="K1231" t="n">
         <v>75289854608</v>
       </c>
+      <c r="L1231" t="n">
+        <v>80227375300</v>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
@@ -52062,9 +52377,18 @@
       <c r="H1237" t="n">
         <v>7919.558398302217</v>
       </c>
+      <c r="I1237" t="n">
+        <v>7906.262233712592</v>
+      </c>
+      <c r="J1237" t="n">
+        <v>0.1678902272186696</v>
+      </c>
       <c r="K1237" t="n">
         <v>76513486683</v>
       </c>
+      <c r="L1237" t="n">
+        <v>80413756542</v>
+      </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
@@ -52095,9 +52419,18 @@
       <c r="H1238" t="n">
         <v>7943.324114761834</v>
       </c>
+      <c r="I1238" t="n">
+        <v>7953.242716231125</v>
+      </c>
+      <c r="J1238" t="n">
+        <v>-0.1248671378127289</v>
+      </c>
       <c r="K1238" t="n">
         <v>76327711628</v>
       </c>
+      <c r="L1238" t="n">
+        <v>80166503963</v>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -52128,9 +52461,18 @@
       <c r="H1239" t="n">
         <v>7955.559478104915</v>
       </c>
+      <c r="I1239" t="n">
+        <v>7909.203600403664</v>
+      </c>
+      <c r="J1239" t="n">
+        <v>0.5826853262656114</v>
+      </c>
       <c r="K1239" t="n">
         <v>76599290187</v>
       </c>
+      <c r="L1239" t="n">
+        <v>80600262557</v>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -52161,8 +52503,17 @@
       <c r="H1240" t="n">
         <v>7950.376677212264</v>
       </c>
+      <c r="I1240" t="n">
+        <v>7947.551867358767</v>
+      </c>
+      <c r="J1240" t="n">
+        <v>0.03553051595144473</v>
+      </c>
       <c r="K1240" t="n">
         <v>76529452691</v>
+      </c>
+      <c r="L1240" t="n">
+        <v>80416954708</v>
       </c>
     </row>
     <row r="1241">

--- a/master-slave/outputs/exp1-full/runs_delta.xlsx
+++ b/master-slave/outputs/exp1-full/runs_delta.xlsx
@@ -47589,18 +47589,9 @@
       <c r="H1123" t="n">
         <v>1771.763056955113</v>
       </c>
-      <c r="I1123" t="n">
-        <v>1779.000878365724</v>
-      </c>
-      <c r="J1123" t="n">
-        <v>-0.4085095567490571</v>
-      </c>
       <c r="K1123" t="n">
         <v>58184281775</v>
       </c>
-      <c r="L1123" t="n">
-        <v>60471533318</v>
-      </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -47631,18 +47622,9 @@
       <c r="H1124" t="n">
         <v>1763.5844050743</v>
       </c>
-      <c r="I1124" t="n">
-        <v>1771.506857743069</v>
-      </c>
-      <c r="J1124" t="n">
-        <v>-0.4492244684163675</v>
-      </c>
       <c r="K1124" t="n">
         <v>58356516054</v>
       </c>
-      <c r="L1124" t="n">
-        <v>60447161693</v>
-      </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
@@ -48051,18 +48033,9 @@
       <c r="H1134" t="n">
         <v>1733.720824201108</v>
       </c>
-      <c r="I1134" t="n">
-        <v>1740.796072994495</v>
-      </c>
-      <c r="J1134" t="n">
-        <v>-0.4080961994932254</v>
-      </c>
       <c r="K1134" t="n">
         <v>58755870420</v>
       </c>
-      <c r="L1134" t="n">
-        <v>61540538472</v>
-      </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -49017,18 +48990,9 @@
       <c r="H1157" t="n">
         <v>1715.978513023062</v>
       </c>
-      <c r="I1157" t="n">
-        <v>1727.081260303168</v>
-      </c>
-      <c r="J1157" t="n">
-        <v>-0.6470213464704755</v>
-      </c>
       <c r="K1157" t="n">
         <v>59610645003</v>
       </c>
-      <c r="L1157" t="n">
-        <v>62453388995</v>
-      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -49605,18 +49569,9 @@
       <c r="H1171" t="n">
         <v>3733.340975642415</v>
       </c>
-      <c r="I1171" t="n">
-        <v>3752.059186104953</v>
-      </c>
-      <c r="J1171" t="n">
-        <v>-0.5013796110417464</v>
-      </c>
       <c r="K1171" t="n">
         <v>54951260017</v>
       </c>
-      <c r="L1171" t="n">
-        <v>57452622269</v>
-      </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
@@ -49857,18 +49812,9 @@
       <c r="H1177" t="n">
         <v>3700.833521391454</v>
       </c>
-      <c r="I1177" t="n">
-        <v>3723.618060129096</v>
-      </c>
-      <c r="J1177" t="n">
-        <v>-0.6156596508852229</v>
-      </c>
       <c r="K1177" t="n">
         <v>54676570942</v>
       </c>
-      <c r="L1177" t="n">
-        <v>56904516140</v>
-      </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -52545,9 +52491,18 @@
       <c r="H1241" t="n">
         <v>7986.487880541967</v>
       </c>
+      <c r="I1241" t="n">
+        <v>7986.487880541967</v>
+      </c>
+      <c r="J1241" t="n">
+        <v>0</v>
+      </c>
       <c r="K1241" t="n">
         <v>76532951156</v>
       </c>
+      <c r="L1241" t="n">
+        <v>80444967741</v>
+      </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -52788,9 +52743,18 @@
       <c r="H1247" t="n">
         <v>13792.6847418359</v>
       </c>
+      <c r="I1247" t="n">
+        <v>13758.28972091187</v>
+      </c>
+      <c r="J1247" t="n">
+        <v>0.2493714716737141</v>
+      </c>
       <c r="K1247" t="n">
         <v>85213459519</v>
       </c>
+      <c r="L1247" t="n">
+        <v>88364124041</v>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
@@ -52821,9 +52785,18 @@
       <c r="H1248" t="n">
         <v>13902.39967882472</v>
       </c>
+      <c r="I1248" t="n">
+        <v>13634.10987291107</v>
+      </c>
+      <c r="J1248" t="n">
+        <v>1.929809328689449</v>
+      </c>
       <c r="K1248" t="n">
         <v>85032951275</v>
       </c>
+      <c r="L1248" t="n">
+        <v>88295050927</v>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
@@ -52854,9 +52827,18 @@
       <c r="H1249" t="n">
         <v>13692.73525325906</v>
       </c>
+      <c r="I1249" t="n">
+        <v>13672.59891564304</v>
+      </c>
+      <c r="J1249" t="n">
+        <v>0.1470585477888673</v>
+      </c>
       <c r="K1249" t="n">
         <v>85080048703</v>
       </c>
+      <c r="L1249" t="n">
+        <v>88226035625</v>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
@@ -52887,9 +52869,18 @@
       <c r="H1250" t="n">
         <v>13803.04652872523</v>
       </c>
+      <c r="I1250" t="n">
+        <v>13731.80646650405</v>
+      </c>
+      <c r="J1250" t="n">
+        <v>0.5161183951161206</v>
+      </c>
       <c r="K1250" t="n">
         <v>85220533676</v>
       </c>
+      <c r="L1250" t="n">
+        <v>88558323031</v>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
@@ -52920,9 +52911,18 @@
       <c r="H1251" t="n">
         <v>13754.97651905488</v>
       </c>
+      <c r="I1251" t="n">
+        <v>13716.71489374352</v>
+      </c>
+      <c r="J1251" t="n">
+        <v>0.278165689765873</v>
+      </c>
       <c r="K1251" t="n">
         <v>85037548987</v>
       </c>
+      <c r="L1251" t="n">
+        <v>88656853692</v>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
@@ -53163,9 +53163,18 @@
       <c r="H1257" t="n">
         <v>13890.68695476892</v>
       </c>
+      <c r="I1257" t="n">
+        <v>13846.06701462474</v>
+      </c>
+      <c r="J1257" t="n">
+        <v>0.3212219834012945</v>
+      </c>
       <c r="K1257" t="n">
         <v>84805062427</v>
       </c>
+      <c r="L1257" t="n">
+        <v>88009688487</v>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
@@ -53196,9 +53205,18 @@
       <c r="H1258" t="n">
         <v>13944.30239762487</v>
       </c>
+      <c r="I1258" t="n">
+        <v>13910.06011452101</v>
+      </c>
+      <c r="J1258" t="n">
+        <v>0.2455646910646981</v>
+      </c>
       <c r="K1258" t="n">
         <v>84895443412</v>
       </c>
+      <c r="L1258" t="n">
+        <v>88396888744</v>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
@@ -53229,9 +53247,18 @@
       <c r="H1259" t="n">
         <v>13866.05475651512</v>
       </c>
+      <c r="I1259" t="n">
+        <v>13795.53591394356</v>
+      </c>
+      <c r="J1259" t="n">
+        <v>0.5085717877929135</v>
+      </c>
       <c r="K1259" t="n">
         <v>84729464406</v>
       </c>
+      <c r="L1259" t="n">
+        <v>87946430898</v>
+      </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
@@ -53262,9 +53289,18 @@
       <c r="H1260" t="n">
         <v>13823.66169038169</v>
       </c>
+      <c r="I1260" t="n">
+        <v>13755.21806655601</v>
+      </c>
+      <c r="J1260" t="n">
+        <v>0.4951193494072865</v>
+      </c>
       <c r="K1260" t="n">
         <v>84892314006</v>
       </c>
+      <c r="L1260" t="n">
+        <v>88381184495</v>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
@@ -53295,9 +53331,18 @@
       <c r="H1261" t="n">
         <v>13967.2496200948</v>
       </c>
+      <c r="I1261" t="n">
+        <v>13891.35496672513</v>
+      </c>
+      <c r="J1261" t="n">
+        <v>0.5433757929011861</v>
+      </c>
       <c r="K1261" t="n">
         <v>84873618697</v>
       </c>
+      <c r="L1261" t="n">
+        <v>88339471935</v>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -53538,9 +53583,18 @@
       <c r="H1267" t="n">
         <v>13988.82655717067</v>
       </c>
+      <c r="I1267" t="n">
+        <v>14028.1256414445</v>
+      </c>
+      <c r="J1267" t="n">
+        <v>-0.2809319574677445</v>
+      </c>
       <c r="K1267" t="n">
         <v>84977695676</v>
       </c>
+      <c r="L1267" t="n">
+        <v>88311267542</v>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -53571,9 +53625,18 @@
       <c r="H1268" t="n">
         <v>13956.88671931398</v>
       </c>
+      <c r="I1268" t="n">
+        <v>14022.36425478705</v>
+      </c>
+      <c r="J1268" t="n">
+        <v>-0.4691414123356567</v>
+      </c>
       <c r="K1268" t="n">
         <v>85125431428</v>
       </c>
+      <c r="L1268" t="n">
+        <v>88638037887</v>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -53604,9 +53667,18 @@
       <c r="H1269" t="n">
         <v>13973.54880030671</v>
       </c>
+      <c r="I1269" t="n">
+        <v>13869.3144906734</v>
+      </c>
+      <c r="J1269" t="n">
+        <v>0.7459401410686876</v>
+      </c>
       <c r="K1269" t="n">
         <v>84711549331</v>
       </c>
+      <c r="L1269" t="n">
+        <v>88180720163</v>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
@@ -53637,8 +53709,17 @@
       <c r="H1270" t="n">
         <v>13884.74136432512</v>
       </c>
+      <c r="I1270" t="n">
+        <v>13847.1386784641</v>
+      </c>
+      <c r="J1270" t="n">
+        <v>0.2708202110097411</v>
+      </c>
       <c r="K1270" t="n">
         <v>85024467954</v>
+      </c>
+      <c r="L1270" t="n">
+        <v>88078850334</v>
       </c>
     </row>
     <row r="1271">

--- a/master-slave/outputs/exp1-full/runs_delta.xlsx
+++ b/master-slave/outputs/exp1-full/runs_delta.xlsx
@@ -53751,9 +53751,18 @@
       <c r="H1271" t="n">
         <v>14004.07750832415</v>
       </c>
+      <c r="I1271" t="n">
+        <v>13986.06619994844</v>
+      </c>
+      <c r="J1271" t="n">
+        <v>0.1286147435631314</v>
+      </c>
       <c r="K1271" t="n">
         <v>84960770785</v>
       </c>
+      <c r="L1271" t="n">
+        <v>88468564648</v>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -53994,9 +54003,18 @@
       <c r="H1277" t="n">
         <v>13822.90852567027</v>
       </c>
+      <c r="I1277" t="n">
+        <v>13781.63862821863</v>
+      </c>
+      <c r="J1277" t="n">
+        <v>0.2985616042745469</v>
+      </c>
       <c r="K1277" t="n">
         <v>84060550239</v>
       </c>
+      <c r="L1277" t="n">
+        <v>88078178828</v>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
@@ -54027,9 +54045,18 @@
       <c r="H1278" t="n">
         <v>13924.65526620875</v>
       </c>
+      <c r="I1278" t="n">
+        <v>13907.74757096483</v>
+      </c>
+      <c r="J1278" t="n">
+        <v>0.1214227204960312</v>
+      </c>
       <c r="K1278" t="n">
         <v>83950399092</v>
       </c>
+      <c r="L1278" t="n">
+        <v>88365370746</v>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
@@ -54060,9 +54087,18 @@
       <c r="H1279" t="n">
         <v>13880.26909240934</v>
       </c>
+      <c r="I1279" t="n">
+        <v>13843.7242624635</v>
+      </c>
+      <c r="J1279" t="n">
+        <v>0.2632861776853122</v>
+      </c>
       <c r="K1279" t="n">
         <v>84153254946</v>
       </c>
+      <c r="L1279" t="n">
+        <v>87910897416</v>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
@@ -54093,9 +54129,18 @@
       <c r="H1280" t="n">
         <v>13934.59163606396</v>
       </c>
+      <c r="I1280" t="n">
+        <v>13781.29925466749</v>
+      </c>
+      <c r="J1280" t="n">
+        <v>1.100085208092781</v>
+      </c>
       <c r="K1280" t="n">
         <v>84031224140</v>
       </c>
+      <c r="L1280" t="n">
+        <v>88277283958</v>
+      </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
@@ -54126,8 +54171,17 @@
       <c r="H1281" t="n">
         <v>13715.36838845595</v>
       </c>
+      <c r="I1281" t="n">
+        <v>13661.87422177441</v>
+      </c>
+      <c r="J1281" t="n">
+        <v>0.390030841071427</v>
+      </c>
       <c r="K1281" t="n">
         <v>83789983201</v>
+      </c>
+      <c r="L1281" t="n">
+        <v>87963806358</v>
       </c>
     </row>
   </sheetData>

--- a/master-slave/outputs/exp1-full/runs_delta.xlsx
+++ b/master-slave/outputs/exp1-full/runs_delta.xlsx
@@ -47589,9 +47589,18 @@
       <c r="H1123" t="n">
         <v>1771.763056955113</v>
       </c>
+      <c r="I1123" t="n">
+        <v>1779.000878365724</v>
+      </c>
+      <c r="J1123" t="n">
+        <v>-0.4085095567490571</v>
+      </c>
       <c r="K1123" t="n">
         <v>58184281775</v>
       </c>
+      <c r="L1123" t="n">
+        <v>60591070792</v>
+      </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -47622,9 +47631,18 @@
       <c r="H1124" t="n">
         <v>1763.5844050743</v>
       </c>
+      <c r="I1124" t="n">
+        <v>1769.407245125932</v>
+      </c>
+      <c r="J1124" t="n">
+        <v>-0.3301707610295245</v>
+      </c>
       <c r="K1124" t="n">
         <v>58356516054</v>
       </c>
+      <c r="L1124" t="n">
+        <v>60104564798</v>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
@@ -48033,9 +48051,18 @@
       <c r="H1134" t="n">
         <v>1733.720824201108</v>
       </c>
+      <c r="I1134" t="n">
+        <v>1740.796072994495</v>
+      </c>
+      <c r="J1134" t="n">
+        <v>-0.4080961994932254</v>
+      </c>
       <c r="K1134" t="n">
         <v>58755870420</v>
       </c>
+      <c r="L1134" t="n">
+        <v>61525364473</v>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -48990,9 +49017,18 @@
       <c r="H1157" t="n">
         <v>1715.978513023062</v>
       </c>
+      <c r="I1157" t="n">
+        <v>1724.119304384219</v>
+      </c>
+      <c r="J1157" t="n">
+        <v>-0.4744110313371717</v>
+      </c>
       <c r="K1157" t="n">
         <v>59610645003</v>
       </c>
+      <c r="L1157" t="n">
+        <v>62560256715</v>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -49569,9 +49605,18 @@
       <c r="H1171" t="n">
         <v>3733.340975642415</v>
       </c>
+      <c r="I1171" t="n">
+        <v>3733.675462285691</v>
+      </c>
+      <c r="J1171" t="n">
+        <v>-0.008959445318766752</v>
+      </c>
       <c r="K1171" t="n">
         <v>54951260017</v>
       </c>
+      <c r="L1171" t="n">
+        <v>57648260853</v>
+      </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
@@ -49812,9 +49857,18 @@
       <c r="H1177" t="n">
         <v>3700.833521391454</v>
       </c>
+      <c r="I1177" t="n">
+        <v>3692.866111767557</v>
+      </c>
+      <c r="J1177" t="n">
+        <v>0.2152868962584619</v>
+      </c>
       <c r="K1177" t="n">
         <v>54676570942</v>
       </c>
+      <c r="L1177" t="n">
+        <v>57000101969</v>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -49930,16 +49984,16 @@
         <v>3701.038233464449</v>
       </c>
       <c r="I1180" t="n">
-        <v>3715.358974128856</v>
+        <v>3709.466388249887</v>
       </c>
       <c r="J1180" t="n">
-        <v>-0.3869384686415851</v>
+        <v>-0.2277240669721224</v>
       </c>
       <c r="K1180" t="n">
         <v>54950125042</v>
       </c>
       <c r="L1180" t="n">
-        <v>57463623038</v>
+        <v>57506645043</v>
       </c>
     </row>
     <row r="1181">
@@ -53626,16 +53680,16 @@
         <v>13956.88671931398</v>
       </c>
       <c r="I1268" t="n">
-        <v>14022.36425478705</v>
+        <v>14096.06715784748</v>
       </c>
       <c r="J1268" t="n">
-        <v>-0.4691414123356567</v>
+        <v>-0.9972169390821458</v>
       </c>
       <c r="K1268" t="n">
         <v>85125431428</v>
       </c>
       <c r="L1268" t="n">
-        <v>88638037887</v>
+        <v>88684519963</v>
       </c>
     </row>
     <row r="1269">

--- a/master-slave/outputs/exp1-full/runs_delta.xlsx
+++ b/master-slave/outputs/exp1-full/runs_delta.xlsx
@@ -53680,16 +53680,16 @@
         <v>13956.88671931398</v>
       </c>
       <c r="I1268" t="n">
-        <v>14096.06715784748</v>
+        <v>14028.94552452589</v>
       </c>
       <c r="J1268" t="n">
-        <v>-0.9972169390821458</v>
+        <v>-0.5162956944559535</v>
       </c>
       <c r="K1268" t="n">
         <v>85125431428</v>
       </c>
       <c r="L1268" t="n">
-        <v>88684519963</v>
+        <v>88631670848</v>
       </c>
     </row>
     <row r="1269">
